--- a/Session 6 - Open Addressing With Double Hashing/Answers/S_9.xlsx
+++ b/Session 6 - Open Addressing With Double Hashing/Answers/S_9.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\varin\Documents\Python\DataScienceClub\Pro_2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\varin\Documents\Data Structure Git\Data-Structure-Library-1402\Session 6 - Open Addressing With Double Hashing\Answers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E1CAF2-207F-47C3-9A3B-48E05CD19A75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BFAB9CF-FE2F-478A-BCCF-2DBA50AFB721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t xml:space="preserve">Student Name </t>
   </si>
@@ -62,12 +62,6 @@
   </si>
   <si>
     <t>(time scale, ms/sec/...)</t>
-  </si>
-  <si>
-    <t>محمدرضا امینی</t>
-  </si>
-  <si>
-    <t>سید محمد مهدی رضوی</t>
   </si>
   <si>
     <t>Windows 11</t>
@@ -447,24 +441,16 @@
       <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" ht="22.5" customHeight="1">
-      <c r="A2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="7">
-        <v>402222073</v>
-      </c>
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
     </row>
     <row r="3" spans="1:6" ht="18.600000000000001">
-      <c r="A3" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="7">
-        <v>402222020</v>
-      </c>
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -500,13 +486,13 @@
     </row>
     <row r="6" spans="1:6" ht="22.5" customHeight="1">
       <c r="A6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>16</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>18</v>
       </c>
       <c r="D6" s="6">
         <v>8</v>
@@ -526,7 +512,7 @@
     </row>
     <row r="8" spans="1:6" ht="26.25" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>8</v>
@@ -538,7 +524,7 @@
     </row>
     <row r="9" spans="1:6" ht="22.5" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B9" s="6">
         <v>100000</v>
@@ -580,7 +566,7 @@
         <v>10.737643003463701</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="22.5" customHeight="1">
@@ -597,7 +583,7 @@
         <v>4.6393339633941597</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="22.5" customHeight="1">
@@ -614,7 +600,7 @@
         <v>5.7130465507507298</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="22.5" customHeight="1"/>
